--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_appointments_by_tretspef-Users_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_appointments_by_tretspef-Users_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -444,176 +444,176 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colorectal Surgery Service</t>
+          <t>Transplant Surgery Service</t>
         </is>
       </c>
       <c r="B4">
-        <v>827</v>
+        <v>41</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>1.37</v>
+        <v>3.26</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>545</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hepatobiliary and Pancreatic Surgery Service</t>
+          <t>Colorectal Surgery Service</t>
         </is>
       </c>
       <c r="B5">
-        <v>64</v>
+        <v>827</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>31</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Upper Gastrointenstinal Surgery Service</t>
+          <t>Hepatobiliary and Pancreatic Surgery Service</t>
         </is>
       </c>
       <c r="B6">
-        <v>141</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>89</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Vascular Surgery Service</t>
+          <t>Upper Gastrointenstinal Surgery Service</t>
         </is>
       </c>
       <c r="B7">
-        <v>634</v>
+        <v>141</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7">
-        <v>1.56</v>
+        <v>1.12</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>344</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Spinal Surgery Service</t>
+          <t>Vascular Surgery Service</t>
         </is>
       </c>
       <c r="B8">
-        <v>401</v>
+        <v>634</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>2.12</v>
+        <v>1.56</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>175</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trauma and Orthopaedic Service</t>
+          <t>Spinal Surgery Service</t>
         </is>
       </c>
       <c r="B9">
-        <v>65476</v>
+        <v>401</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>4.91</v>
+        <v>2.12</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>216</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>17633</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ear Nose and Throat Service</t>
+          <t>Trauma and Orthopaedic Service</t>
         </is>
       </c>
       <c r="B10">
-        <v>2449</v>
+        <v>63514</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>4.75</v>
+        <v>4.17</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="G10">
-        <v>1182</v>
+        <v>17426</v>
       </c>
     </row>
     <row r="11">
@@ -698,344 +698,344 @@
         </is>
       </c>
       <c r="B14">
-        <v>484</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>255</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Maxillofacial Surgery Service</t>
+          <t>Neurosurgical Service</t>
         </is>
       </c>
       <c r="B15">
-        <v>536</v>
+        <v>661</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G15">
-        <v>258</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Neurosurgical Service</t>
+          <t>Plastic Surgery Service</t>
         </is>
       </c>
       <c r="B16">
-        <v>661</v>
+        <v>1061</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>2.09</v>
+        <v>3</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G16">
-        <v>301</v>
+        <v>357</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Plastic Surgery Service</t>
+          <t>Cardiothoracic Surgery Service</t>
         </is>
       </c>
       <c r="B17">
-        <v>1061</v>
+        <v>53</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>1.09</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>357</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Burns Care Service</t>
+          <t>Cardiac Surgery Service</t>
         </is>
       </c>
       <c r="B18">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>6.07</v>
+        <v>1.01</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cardiothoracic Surgery Service</t>
+          <t>Thoracic Surgery Service</t>
         </is>
       </c>
       <c r="B19">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
       <c r="D19">
-        <v>1.09</v>
+        <v>0.93</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cardiac Surgery Service</t>
+          <t>Cardiothoracic Transplantation Service</t>
         </is>
       </c>
       <c r="B20">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D20">
-        <v>1.01</v>
+        <v>15.7</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G20">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Thoracic Surgery Service</t>
+          <t>Emergency Medicine Service</t>
         </is>
       </c>
       <c r="B21">
-        <v>38</v>
+        <v>378</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G21">
-        <v>21</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cardiothoracic Transplantation Service</t>
+          <t>Anaesthetic Service</t>
         </is>
       </c>
       <c r="B22">
-        <v>56</v>
+        <v>480</v>
       </c>
       <c r="C22">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>15.7</v>
+        <v>0.62</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>375</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Anaesthetic Service</t>
+          <t>Pain Management Service</t>
         </is>
       </c>
       <c r="B23">
-        <v>480</v>
+        <v>1186</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23">
-        <v>0.62</v>
+        <v>2.43</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G23">
-        <v>375</v>
+        <v>473</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pain Management Service</t>
+          <t>Paediatric Trauma and Orthopaedic Service</t>
         </is>
       </c>
       <c r="B24">
-        <v>1186</v>
+        <v>18</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>2.43</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>473</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Paediatric Trauma and Orthopaedic Service</t>
+          <t>Paediatric Ear Nose and Throat Service</t>
         </is>
       </c>
       <c r="B25">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
-      <c r="D25">
-        <v>0.5600000000000001</v>
-      </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Paediatric Ear Nose and Throat Service</t>
+          <t>Paediatric Ophthalmology Service</t>
         </is>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>2.14</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Paediatric Ophthalmology Service</t>
+          <t>General Internal Medicine Service</t>
         </is>
       </c>
       <c r="B27">
-        <v>16</v>
+        <v>3118</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27">
-        <v>2.14</v>
+        <v>9.06</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>7</v>
+        <v>170</v>
       </c>
       <c r="G27">
-        <v>7</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="28">
@@ -1191,48 +1191,48 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Blood and Marrow Transplantation Service</t>
+          <t>Diabetes Service</t>
         </is>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>929</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D34">
+        <v>5.22</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Haemophilia Service</t>
+          <t>Blood and Marrow Transplantation Service</t>
         </is>
       </c>
       <c r="B35">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>2</v>
-      </c>
-      <c r="D35">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1363,448 +1363,448 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Allergy Service</t>
+          <t>Intermediate Care Service</t>
         </is>
       </c>
       <c r="B41">
-        <v>77</v>
+        <v>2238</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D41">
-        <v>13.43</v>
+        <v>22.54</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="F41">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="G41">
-        <v>14</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Intermediate Care Service</t>
+          <t>Cardiology Service</t>
         </is>
       </c>
       <c r="B42">
-        <v>1796</v>
+        <v>4309</v>
       </c>
       <c r="C42">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D42">
-        <v>20.92</v>
+        <v>2.05</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42">
-        <v>121</v>
+        <v>29</v>
       </c>
       <c r="G42">
-        <v>136</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cardiology Service</t>
+          <t>Clinical Microbiology Service</t>
         </is>
       </c>
       <c r="B43">
-        <v>4309</v>
+        <v>10</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>2.05</v>
+        <v>0.79</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="G43">
-        <v>2015</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Clinical Microbiology Service</t>
+          <t>Spinal Injuries Service</t>
         </is>
       </c>
       <c r="B44">
+        <v>34</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44">
+        <v>2.63</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
         <v>10</v>
       </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
-        <v>0.79</v>
-      </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <v>3</v>
-      </c>
       <c r="G44">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Spinal Injuries Service</t>
+          <t>Anticoagulant Service</t>
         </is>
       </c>
       <c r="B45">
-        <v>34</v>
+        <v>2976</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D45">
-        <v>2.63</v>
+        <v>11.68</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="G45">
-        <v>10</v>
+        <v>298</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Anticoagulant Service</t>
+          <t>Sport and Exercise Medicine Service</t>
         </is>
       </c>
       <c r="B46">
-        <v>2976</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>10</v>
-      </c>
-      <c r="D46">
-        <v>11.68</v>
+        <v>4</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F46">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="G46">
-        <v>298</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sport and Exercise Medicine Service</t>
+          <t>Cardiac Rehabilitation Service</t>
         </is>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="D47">
+        <v>7.88</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cardiac Rehabilitation Service</t>
+          <t>Stroke Medicine Service</t>
         </is>
       </c>
       <c r="B48">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="C48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>7.88</v>
+        <v>0.76</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G48">
-        <v>10</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Stroke Medicine Service</t>
+          <t>Transient Ischaemic Attack Service</t>
         </is>
       </c>
       <c r="B49">
-        <v>75</v>
+        <v>141</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
       <c r="D49">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G49">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Transient Ischaemic Attack Service</t>
+          <t>Dermatology Service</t>
         </is>
       </c>
       <c r="B50">
-        <v>141</v>
+        <v>2835</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50">
-        <v>0.51</v>
+        <v>4.19</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="G50">
-        <v>116</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dermatology Service</t>
+          <t>Congenital Heart Disease Service</t>
         </is>
       </c>
       <c r="B51">
-        <v>2835</v>
+        <v>6</v>
       </c>
       <c r="C51">
         <v>3</v>
       </c>
       <c r="D51">
-        <v>4.19</v>
+        <v>2.83</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="F51">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="G51">
-        <v>1118</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Congenital Heart Disease Service</t>
+          <t>Respiratory Physiology Service</t>
         </is>
       </c>
       <c r="B52">
-        <v>6</v>
+        <v>225</v>
       </c>
       <c r="C52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52">
-        <v>2.83</v>
+        <v>1.51</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Respiratory Medicine Service</t>
+          <t>Pulmonary Rehabilitation Service</t>
         </is>
       </c>
       <c r="B53">
-        <v>2504</v>
+        <v>10</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53">
-        <v>4.06</v>
+        <v>1.21</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
       <c r="F53">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="G53">
-        <v>867</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Respiratory Physiology Service</t>
+          <t>Complex Specialised Rehabilitation Service</t>
         </is>
       </c>
       <c r="B54">
-        <v>225</v>
+        <v>16</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D54">
-        <v>1.51</v>
+        <v>5.86</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G54">
-        <v>125</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Complex Specialised Rehabilitation Service</t>
+          <t>Infectious Diseases Service</t>
         </is>
       </c>
       <c r="B55">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D55">
-        <v>5.86</v>
+        <v>2.1</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="F55">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Infectious Diseases Service</t>
+          <t>Tropical Medicine Service</t>
         </is>
       </c>
       <c r="B56">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tropical Medicine Service</t>
+          <t>Genitourinary Medicine Service</t>
         </is>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="E57">
         <v>1</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Genitourinary Medicine Service</t>
+          <t>Renal Medicine Service</t>
         </is>
       </c>
       <c r="B58">
-        <v>11</v>
+        <v>959</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D58">
-        <v>1.17</v>
+        <v>4.14</v>
       </c>
       <c r="E58">
         <v>1</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G58">
-        <v>6</v>
+        <v>259</v>
       </c>
     </row>
     <row r="59">
@@ -1864,619 +1864,694 @@
         </is>
       </c>
       <c r="B61">
-        <v>2659</v>
+        <v>1700</v>
       </c>
       <c r="C61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61">
-        <v>2.98</v>
+        <v>2.29</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
       <c r="F61">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G61">
-        <v>1009</v>
+        <v>762</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Clinical Neurophysiology Service</t>
+          <t>Rheumatology Service</t>
         </is>
       </c>
       <c r="B62">
-        <v>255</v>
+        <v>5236</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62">
-        <v>0.51</v>
+        <v>2.87</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="G62">
-        <v>221</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rheumatology Service</t>
+          <t>Paediatric Service</t>
         </is>
       </c>
       <c r="B63">
-        <v>5236</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>2194</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Paediatric Service</t>
+          <t>Elderly Medicine Service</t>
         </is>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>3208</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Elderly Medicine Service</t>
+          <t>Dental Medicine Service</t>
         </is>
       </c>
       <c r="B65">
-        <v>4137</v>
+        <v>130</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65">
-        <v>4.51</v>
+        <v>2.13</v>
       </c>
       <c r="E65">
         <v>1</v>
       </c>
       <c r="F65">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="G65">
-        <v>1589</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dental Medicine Service</t>
+          <t>Medical Ophthalmology Service</t>
         </is>
       </c>
       <c r="B66">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C66">
         <v>2</v>
       </c>
       <c r="D66">
-        <v>2.13</v>
+        <v>3.82</v>
       </c>
       <c r="E66">
         <v>1</v>
       </c>
       <c r="F66">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G66">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Medical Ophthalmology Service</t>
+          <t>Gynaecology Service</t>
         </is>
       </c>
       <c r="B67">
-        <v>125</v>
+        <v>2016</v>
       </c>
       <c r="C67">
         <v>2</v>
       </c>
       <c r="D67">
-        <v>3.82</v>
+        <v>1.82</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G67">
-        <v>57</v>
+        <v>904</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Obstetrics Service</t>
+          <t>Gynaecological Oncology Service</t>
         </is>
       </c>
       <c r="B68">
-        <v>4</v>
+        <v>199</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="E68">
         <v>1</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Gynaecology Service</t>
+          <t>Physiotherapy Service</t>
         </is>
       </c>
       <c r="B69">
-        <v>2016</v>
+        <v>26485</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D69">
-        <v>1.82</v>
+        <v>5.1</v>
       </c>
       <c r="E69">
         <v>1</v>
       </c>
       <c r="F69">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="G69">
-        <v>904</v>
+        <v>5351</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Gynaecological Oncology Service</t>
+          <t>Occupational Therapy Service</t>
         </is>
       </c>
       <c r="B70">
-        <v>199</v>
+        <v>2747</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D70">
-        <v>1.66</v>
+        <v>6.81</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="G70">
-        <v>115</v>
+        <v>616</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Physiotherapy Service</t>
+          <t>Podiatry Service</t>
         </is>
       </c>
       <c r="B71">
-        <v>26485</v>
+        <v>1509</v>
       </c>
       <c r="C71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D71">
-        <v>5.1</v>
+        <v>4.54</v>
       </c>
       <c r="E71">
         <v>1</v>
       </c>
       <c r="F71">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="G71">
-        <v>5351</v>
+        <v>372</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Occupational Therapy Service</t>
+          <t>Dietetics Service</t>
         </is>
       </c>
       <c r="B72">
-        <v>2747</v>
+        <v>622</v>
       </c>
       <c r="C72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D72">
-        <v>6.81</v>
+        <v>3.49</v>
       </c>
       <c r="E72">
         <v>1</v>
       </c>
       <c r="F72">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="G72">
-        <v>616</v>
+        <v>229</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Speech and Language Therapy Service</t>
+          <t>Orthoptics Service</t>
         </is>
       </c>
       <c r="B73">
-        <v>211</v>
+        <v>328</v>
       </c>
       <c r="C73">
         <v>2</v>
       </c>
       <c r="D73">
-        <v>2.67</v>
+        <v>1.31</v>
       </c>
       <c r="E73">
         <v>1</v>
       </c>
       <c r="F73">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G73">
-        <v>87</v>
+        <v>178</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Orthoptics Service</t>
+          <t>Clinical Psychology Service</t>
         </is>
       </c>
       <c r="B74">
-        <v>328</v>
+        <v>97</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D74">
-        <v>1.31</v>
+        <v>7.69</v>
       </c>
       <c r="E74">
         <v>1</v>
       </c>
       <c r="F74">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G74">
-        <v>178</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Clinical Psychology Service</t>
+          <t>Prosthetics Service</t>
         </is>
       </c>
       <c r="B75">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D75">
-        <v>7.69</v>
+        <v>0.58</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="F75">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G75">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Prosthetics Service</t>
+          <t>Orthotics Service</t>
         </is>
       </c>
       <c r="B76">
-        <v>6</v>
+        <v>481</v>
       </c>
       <c r="C76">
         <v>2</v>
       </c>
       <c r="D76">
-        <v>0.58</v>
+        <v>1.49</v>
       </c>
       <c r="E76">
         <v>1</v>
       </c>
       <c r="F76">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Podiatric Surgery Service</t>
+          <t>Optometry Service</t>
         </is>
       </c>
       <c r="B77">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77">
-        <v>2.37</v>
+        <v>0.9</v>
       </c>
       <c r="E77">
         <v>1</v>
       </c>
       <c r="F77">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G77">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Learning Disability Service</t>
+          <t>Podiatric Surgery Service</t>
         </is>
       </c>
       <c r="B78">
-        <v>334</v>
+        <v>44</v>
       </c>
       <c r="C78">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D78">
-        <v>14.03</v>
+        <v>2.37</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="F78">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="G78">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Child and Adolescent Psychiatry Service</t>
+          <t>Learning Disability Service</t>
         </is>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>334</v>
       </c>
       <c r="C79">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="D79">
+        <v>14.03</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F79">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Old Age Psychiatry Service</t>
+          <t>Child and Adolescent Psychiatry Service</t>
         </is>
       </c>
       <c r="B80">
-        <v>1422</v>
+        <v>3</v>
       </c>
       <c r="C80">
         <v>3</v>
       </c>
-      <c r="D80">
-        <v>5.53</v>
-      </c>
       <c r="E80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F80">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="G80">
-        <v>464</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Liaison Psychiatry Service</t>
+          <t>Medical Psychotherapy Service</t>
         </is>
       </c>
       <c r="B81">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D81">
-        <v>3.42</v>
+        <v>1.73</v>
       </c>
       <c r="E81">
         <v>1</v>
       </c>
       <c r="F81">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G81">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Clinical Oncology Service</t>
+          <t>Old Age Psychiatry Service</t>
         </is>
       </c>
       <c r="B82">
-        <v>586</v>
+        <v>1422</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D82">
-        <v>6.61</v>
+        <v>5.53</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="G82">
-        <v>133</v>
+        <v>464</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Interventional Radiology Service</t>
+          <t>Liaison Psychiatry Service</t>
         </is>
       </c>
       <c r="B83">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D83">
-        <v>0.27</v>
+        <v>3.42</v>
       </c>
       <c r="E83">
         <v>1</v>
       </c>
       <c r="F83">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G83">
-        <v>172</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging Service</t>
+          <t>Clinical Oncology Service</t>
         </is>
       </c>
       <c r="B84">
-        <v>5698</v>
+        <v>586</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D84">
-        <v>1.82</v>
+        <v>6.61</v>
       </c>
       <c r="E84">
         <v>1</v>
       </c>
       <c r="F84">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G84">
-        <v>2933</v>
+        <v>133</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>Interventional Radiology Service</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>183</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85">
+        <v>0.27</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85">
+        <v>3</v>
+      </c>
+      <c r="G85">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Diagnostic Imaging Service</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>5698</v>
+      </c>
+      <c r="C86">
+        <v>2</v>
+      </c>
+      <c r="D86">
+        <v>1.82</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+      <c r="F86">
+        <v>41</v>
+      </c>
+      <c r="G86">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>Chemical Pathology Service</t>
         </is>
       </c>
-      <c r="B85">
+      <c r="B87">
         <v>101</v>
       </c>
-      <c r="C85">
-        <v>3</v>
-      </c>
-      <c r="D85">
+      <c r="C87">
+        <v>3</v>
+      </c>
+      <c r="D87">
         <v>1.82</v>
       </c>
-      <c r="E85">
-        <v>1</v>
-      </c>
-      <c r="F85">
+      <c r="E87">
+        <v>1</v>
+      </c>
+      <c r="F87">
         <v>7</v>
       </c>
-      <c r="G85">
+      <c r="G87">
         <v>37</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Audiology Service</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>1883</v>
+      </c>
+      <c r="C88">
+        <v>2</v>
+      </c>
+      <c r="D88">
+        <v>1.79</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="F88">
+        <v>21</v>
+      </c>
+      <c r="G88">
+        <v>787</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_appointments_by_tretspef-Users_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_appointments_by_tretspef-Users_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -598,13 +598,13 @@
         </is>
       </c>
       <c r="B10">
-        <v>63514</v>
+        <v>56862</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>4.17</v>
+        <v>3.48</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -613,742 +613,742 @@
         <v>201</v>
       </c>
       <c r="G10">
-        <v>17426</v>
+        <v>16816</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ophthalmology Service</t>
+          <t>Ear Nose and Throat Service</t>
         </is>
       </c>
       <c r="B11">
-        <v>11730</v>
+        <v>2449</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>4.09</v>
+        <v>4.75</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>40</v>
+        <v>152</v>
       </c>
       <c r="G11">
-        <v>3308</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oral Surgery Service</t>
+          <t>Ophthalmology Service</t>
         </is>
       </c>
       <c r="B12">
-        <v>675</v>
+        <v>11730</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>1.43</v>
+        <v>4.09</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="G12">
-        <v>350</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Restorative Dentistry Service</t>
+          <t>Oral Surgery Service</t>
         </is>
       </c>
       <c r="B13">
-        <v>331</v>
+        <v>675</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>3.89</v>
+        <v>1.43</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G13">
-        <v>86</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Orthodontic Service</t>
+          <t>Restorative Dentistry Service</t>
         </is>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>331</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Neurosurgical Service</t>
+          <t>Orthodontic Service</t>
         </is>
       </c>
       <c r="B15">
-        <v>661</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>301</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Plastic Surgery Service</t>
+          <t>Maxillofacial Surgery Service</t>
         </is>
       </c>
       <c r="B16">
-        <v>1061</v>
+        <v>536</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>1.98</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16">
-        <v>357</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cardiothoracic Surgery Service</t>
+          <t>Neurosurgical Service</t>
         </is>
       </c>
       <c r="B17">
-        <v>53</v>
+        <v>661</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17">
-        <v>1.09</v>
+        <v>2.09</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="G17">
-        <v>33</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cardiac Surgery Service</t>
+          <t>Plastic Surgery Service</t>
         </is>
       </c>
       <c r="B18">
-        <v>61</v>
+        <v>1061</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G18">
-        <v>35</v>
+        <v>357</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Thoracic Surgery Service</t>
+          <t>Burns Care Service</t>
         </is>
       </c>
       <c r="B19">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>0.93</v>
+        <v>6.07</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G19">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cardiothoracic Transplantation Service</t>
+          <t>Cardiothoracic Surgery Service</t>
         </is>
       </c>
       <c r="B20">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C20">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>15.7</v>
+        <v>1.09</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Emergency Medicine Service</t>
+          <t>Cardiac Surgery Service</t>
         </is>
       </c>
       <c r="B21">
-        <v>378</v>
+        <v>61</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G21">
-        <v>268</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Anaesthetic Service</t>
+          <t>Thoracic Surgery Service</t>
         </is>
       </c>
       <c r="B22">
-        <v>480</v>
+        <v>38</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>0.62</v>
+        <v>0.93</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22">
-        <v>375</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pain Management Service</t>
+          <t>Cardiothoracic Transplantation Service</t>
         </is>
       </c>
       <c r="B23">
-        <v>1186</v>
+        <v>56</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D23">
-        <v>2.43</v>
+        <v>15.7</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G23">
-        <v>473</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Paediatric Trauma and Orthopaedic Service</t>
+          <t>Emergency Medicine Service</t>
         </is>
       </c>
       <c r="B24">
-        <v>18</v>
+        <v>378</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24">
-        <v>0.5600000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G24">
-        <v>15</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Paediatric Ear Nose and Throat Service</t>
+          <t>Anaesthetic Service</t>
         </is>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>480</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
+      <c r="D25">
+        <v>0.62</v>
+      </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>375</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Paediatric Ophthalmology Service</t>
+          <t>Pain Management Service</t>
         </is>
       </c>
       <c r="B26">
+        <v>1186</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>2.43</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
         <v>16</v>
       </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>2.14</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <v>7</v>
-      </c>
       <c r="G26">
-        <v>7</v>
+        <v>473</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>General Internal Medicine Service</t>
+          <t>Paediatric Trauma and Orthopaedic Service</t>
         </is>
       </c>
       <c r="B27">
-        <v>3118</v>
+        <v>18</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>9.06</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>170</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>1126</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gastroenterology Service</t>
+          <t>Paediatric Ear Nose and Throat Service</t>
         </is>
       </c>
       <c r="B28">
-        <v>1813</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>2</v>
-      </c>
-      <c r="D28">
-        <v>1.74</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>949</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Endocrinology Service</t>
+          <t>Paediatric Ophthalmology Service</t>
         </is>
       </c>
       <c r="B29">
-        <v>586</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G29">
-        <v>269</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Clinical Haematology Service</t>
+          <t>General Internal Medicine Service</t>
         </is>
       </c>
       <c r="B30">
-        <v>1600</v>
+        <v>3118</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30">
-        <v>4.06</v>
+        <v>9.06</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="G30">
-        <v>477</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Clinical Physiology Service</t>
+          <t>Gastroenterology Service</t>
         </is>
       </c>
       <c r="B31">
-        <v>748</v>
+        <v>1813</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>1.08</v>
+        <v>1.74</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G31">
-        <v>502</v>
+        <v>949</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Clinical Pharmacology Service</t>
+          <t>Endocrinology Service</t>
         </is>
       </c>
       <c r="B32">
-        <v>17</v>
+        <v>586</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G32">
-        <v>7</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hepatology Service</t>
+          <t>Clinical Haematology Service</t>
         </is>
       </c>
       <c r="B33">
-        <v>144</v>
+        <v>1600</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33">
-        <v>1.15</v>
+        <v>4.06</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G33">
-        <v>70</v>
+        <v>477</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Diabetes Service</t>
+          <t>Clinical Physiology Service</t>
         </is>
       </c>
       <c r="B34">
-        <v>929</v>
+        <v>748</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>5.22</v>
+        <v>1.08</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="G34">
-        <v>268</v>
+        <v>502</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Blood and Marrow Transplantation Service</t>
+          <t>Clinical Pharmacology Service</t>
         </is>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D35">
+        <v>2.15</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Clinical Genetics Service</t>
+          <t>Hepatology Service</t>
         </is>
       </c>
       <c r="B36">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G36">
-        <v>10</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Clinical Immunology and Allergy Service</t>
+          <t>Diabetes Service</t>
         </is>
       </c>
       <c r="B37">
-        <v>47</v>
+        <v>929</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37">
-        <v>1.81</v>
+        <v>5.22</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="G37">
-        <v>20</v>
+        <v>268</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Rehabilitation Medicine Service</t>
+          <t>Blood and Marrow Transplantation Service</t>
         </is>
       </c>
       <c r="B38">
-        <v>1378</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>4</v>
-      </c>
-      <c r="D38">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>318</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Palliative Medicine Service</t>
+          <t>Clinical Genetics Service</t>
         </is>
       </c>
       <c r="B39">
-        <v>212</v>
+        <v>10</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>12.45</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Clinical Immunology Service</t>
+          <t>Clinical Immunology and Allergy Service</t>
         </is>
       </c>
       <c r="B40">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>2.19</v>
+        <v>1.81</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -1357,320 +1357,320 @@
         <v>7</v>
       </c>
       <c r="G40">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Intermediate Care Service</t>
+          <t>Rehabilitation Medicine Service</t>
         </is>
       </c>
       <c r="B41">
-        <v>2238</v>
+        <v>1378</v>
       </c>
       <c r="C41">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D41">
-        <v>22.54</v>
+        <v>6.2</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="F41">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="G41">
-        <v>168</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cardiology Service</t>
+          <t>Palliative Medicine Service</t>
         </is>
       </c>
       <c r="B42">
-        <v>4309</v>
+        <v>212</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D42">
-        <v>2.05</v>
+        <v>12.45</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="G42">
-        <v>2015</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Clinical Microbiology Service</t>
+          <t>Clinical Immunology Service</t>
         </is>
       </c>
       <c r="B43">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D43">
-        <v>0.79</v>
+        <v>2.19</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G43">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Spinal Injuries Service</t>
+          <t>Allergy Service</t>
         </is>
       </c>
       <c r="B44">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D44">
-        <v>2.63</v>
+        <v>13.43</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
       <c r="F44">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="G44">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Anticoagulant Service</t>
+          <t>Intermediate Care Service</t>
         </is>
       </c>
       <c r="B45">
-        <v>2976</v>
+        <v>2238</v>
       </c>
       <c r="C45">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D45">
-        <v>11.68</v>
+        <v>22.54</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="G45">
-        <v>298</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sport and Exercise Medicine Service</t>
+          <t>Cardiology Service</t>
         </is>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>4309</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <v>2.05</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cardiac Rehabilitation Service</t>
+          <t>Clinical Microbiology Service</t>
         </is>
       </c>
       <c r="B47">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>7.88</v>
+        <v>0.79</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Stroke Medicine Service</t>
+          <t>Spinal Injuries Service</t>
         </is>
       </c>
       <c r="B48">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D48">
-        <v>0.76</v>
+        <v>2.63</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G48">
-        <v>57</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Transient Ischaemic Attack Service</t>
+          <t>Anticoagulant Service</t>
         </is>
       </c>
       <c r="B49">
-        <v>141</v>
+        <v>2976</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D49">
-        <v>0.51</v>
+        <v>11.68</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="G49">
-        <v>116</v>
+        <v>298</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dermatology Service</t>
+          <t>Sport and Exercise Medicine Service</t>
         </is>
       </c>
       <c r="B50">
-        <v>2835</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>3</v>
-      </c>
-      <c r="D50">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="G50">
-        <v>1118</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Congenital Heart Disease Service</t>
+          <t>Cardiac Rehabilitation Service</t>
         </is>
       </c>
       <c r="B51">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D51">
-        <v>2.83</v>
+        <v>7.88</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Respiratory Physiology Service</t>
+          <t>Stroke Medicine Service</t>
         </is>
       </c>
       <c r="B52">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>1.51</v>
+        <v>0.76</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G52">
-        <v>125</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pulmonary Rehabilitation Service</t>
+          <t>Transient Ischaemic Attack Service</t>
         </is>
       </c>
       <c r="B53">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>1.21</v>
+        <v>0.51</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -1679,878 +1679,1078 @@
         <v>4</v>
       </c>
       <c r="G53">
-        <v>6</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Complex Specialised Rehabilitation Service</t>
+          <t>Dermatology Service</t>
         </is>
       </c>
       <c r="B54">
-        <v>16</v>
+        <v>2835</v>
       </c>
       <c r="C54">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D54">
-        <v>5.86</v>
+        <v>4.19</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Infectious Diseases Service</t>
+          <t>Congenital Heart Disease Service</t>
         </is>
       </c>
       <c r="B55">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55">
-        <v>2.1</v>
+        <v>2.83</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="F55">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G55">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tropical Medicine Service</t>
+          <t>Respiratory Medicine Service</t>
         </is>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>2504</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>867</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Genitourinary Medicine Service</t>
+          <t>Respiratory Physiology Service</t>
         </is>
       </c>
       <c r="B57">
-        <v>11</v>
+        <v>225</v>
       </c>
       <c r="C57">
         <v>2</v>
       </c>
       <c r="D57">
-        <v>1.17</v>
+        <v>1.51</v>
       </c>
       <c r="E57">
         <v>1</v>
       </c>
       <c r="F57">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G57">
-        <v>6</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Renal Medicine Service</t>
+          <t>Pulmonary Rehabilitation Service</t>
         </is>
       </c>
       <c r="B58">
-        <v>959</v>
+        <v>10</v>
       </c>
       <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58">
+        <v>1.21</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
         <v>4</v>
       </c>
-      <c r="D58">
-        <v>4.14</v>
-      </c>
-      <c r="E58">
-        <v>1</v>
-      </c>
-      <c r="F58">
-        <v>27</v>
-      </c>
       <c r="G58">
-        <v>259</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Medical Oncology Service</t>
+          <t>Complex Specialised Rehabilitation Service</t>
         </is>
       </c>
       <c r="B59">
-        <v>298</v>
+        <v>16</v>
       </c>
       <c r="C59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D59">
-        <v>6.91</v>
+        <v>5.86</v>
       </c>
       <c r="E59">
         <v>1</v>
       </c>
       <c r="F59">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="G59">
-        <v>73</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Nuclear Medicine Service</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B60">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C60">
         <v>2</v>
       </c>
       <c r="D60">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="E60">
         <v>1</v>
       </c>
       <c r="F60">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G60">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Neurology Service</t>
+          <t>Infectious Diseases Service</t>
         </is>
       </c>
       <c r="B61">
-        <v>1700</v>
+        <v>58</v>
       </c>
       <c r="C61">
         <v>2</v>
       </c>
       <c r="D61">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
       <c r="F61">
+        <v>8</v>
+      </c>
+      <c r="G61">
         <v>26</v>
-      </c>
-      <c r="G61">
-        <v>762</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Rheumatology Service</t>
+          <t>Tropical Medicine Service</t>
         </is>
       </c>
       <c r="B62">
-        <v>5236</v>
+        <v>3</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>2194</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Paediatric Service</t>
+          <t>Genitourinary Medicine Service</t>
         </is>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Elderly Medicine Service</t>
+          <t>Renal Medicine Service</t>
         </is>
       </c>
       <c r="B64">
-        <v>3208</v>
+        <v>959</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D64">
-        <v>4.25</v>
+        <v>4.14</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="F64">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="G64">
-        <v>1345</v>
+        <v>259</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dental Medicine Service</t>
+          <t>Medical Oncology Service</t>
         </is>
       </c>
       <c r="B65">
-        <v>130</v>
+        <v>298</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D65">
-        <v>2.13</v>
+        <v>6.91</v>
       </c>
       <c r="E65">
         <v>1</v>
       </c>
       <c r="F65">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="G65">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Medical Ophthalmology Service</t>
+          <t>Nuclear Medicine Service</t>
         </is>
       </c>
       <c r="B66">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="C66">
         <v>2</v>
       </c>
       <c r="D66">
-        <v>3.82</v>
+        <v>1.46</v>
       </c>
       <c r="E66">
         <v>1</v>
       </c>
       <c r="F66">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="G66">
-        <v>57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Gynaecology Service</t>
+          <t>Neurology Service</t>
         </is>
       </c>
       <c r="B67">
-        <v>2016</v>
+        <v>1700</v>
       </c>
       <c r="C67">
         <v>2</v>
       </c>
       <c r="D67">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G67">
-        <v>904</v>
+        <v>762</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Gynaecological Oncology Service</t>
+          <t>Rheumatology Service</t>
         </is>
       </c>
       <c r="B68">
-        <v>199</v>
+        <v>5236</v>
       </c>
       <c r="C68">
         <v>2</v>
       </c>
       <c r="D68">
-        <v>1.66</v>
+        <v>2.87</v>
       </c>
       <c r="E68">
         <v>1</v>
       </c>
       <c r="F68">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="G68">
-        <v>115</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Physiotherapy Service</t>
+          <t>Paediatric Service</t>
         </is>
       </c>
       <c r="B69">
-        <v>26485</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D69">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <v>1</v>
       </c>
       <c r="F69">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>5351</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Occupational Therapy Service</t>
+          <t>Elderly Medicine Service</t>
         </is>
       </c>
       <c r="B70">
-        <v>2747</v>
+        <v>3208</v>
       </c>
       <c r="C70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D70">
-        <v>6.81</v>
+        <v>4.25</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G70">
-        <v>616</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Podiatry Service</t>
+          <t>Dental Medicine Service</t>
         </is>
       </c>
       <c r="B71">
-        <v>1509</v>
+        <v>130</v>
       </c>
       <c r="C71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D71">
-        <v>4.54</v>
+        <v>2.13</v>
       </c>
       <c r="E71">
         <v>1</v>
       </c>
       <c r="F71">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G71">
-        <v>372</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dietetics Service</t>
+          <t>Medical Ophthalmology Service</t>
         </is>
       </c>
       <c r="B72">
-        <v>622</v>
+        <v>125</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D72">
-        <v>3.49</v>
+        <v>3.82</v>
       </c>
       <c r="E72">
         <v>1</v>
       </c>
       <c r="F72">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G72">
-        <v>229</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Orthoptics Service</t>
+          <t>Obstetrics Service</t>
         </is>
       </c>
       <c r="B73">
-        <v>328</v>
+        <v>4</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>1</v>
       </c>
       <c r="F73">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>178</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Clinical Psychology Service</t>
+          <t>Gynaecology Service</t>
         </is>
       </c>
       <c r="B74">
-        <v>97</v>
+        <v>2016</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D74">
-        <v>7.69</v>
+        <v>1.82</v>
       </c>
       <c r="E74">
         <v>1</v>
       </c>
       <c r="F74">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G74">
-        <v>19</v>
+        <v>904</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Prosthetics Service</t>
+          <t>Gynaecological Oncology Service</t>
         </is>
       </c>
       <c r="B75">
-        <v>6</v>
+        <v>199</v>
       </c>
       <c r="C75">
         <v>2</v>
       </c>
       <c r="D75">
-        <v>0.58</v>
+        <v>1.66</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G75">
-        <v>4</v>
+        <v>115</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Orthotics Service</t>
+          <t>Physiotherapy Service</t>
         </is>
       </c>
       <c r="B76">
-        <v>481</v>
+        <v>26485</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D76">
-        <v>1.49</v>
+        <v>5.1</v>
       </c>
       <c r="E76">
         <v>1</v>
       </c>
       <c r="F76">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="G76">
-        <v>252</v>
+        <v>5351</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Optometry Service</t>
+          <t>Occupational Therapy Service</t>
         </is>
       </c>
       <c r="B77">
-        <v>54</v>
+        <v>2747</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D77">
-        <v>0.9</v>
+        <v>6.81</v>
       </c>
       <c r="E77">
         <v>1</v>
       </c>
       <c r="F77">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="G77">
-        <v>37</v>
+        <v>616</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Podiatric Surgery Service</t>
+          <t>Podiatry Service</t>
         </is>
       </c>
       <c r="B78">
-        <v>44</v>
+        <v>1509</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D78">
-        <v>2.37</v>
+        <v>4.54</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="F78">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G78">
-        <v>15</v>
+        <v>372</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Learning Disability Service</t>
+          <t>Dietetics Service</t>
         </is>
       </c>
       <c r="B79">
-        <v>334</v>
+        <v>622</v>
       </c>
       <c r="C79">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D79">
-        <v>14.03</v>
+        <v>3.49</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="G79">
-        <v>41</v>
+        <v>229</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Child and Adolescent Psychiatry Service</t>
+          <t>Orthoptics Service</t>
         </is>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>328</v>
       </c>
       <c r="C80">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>1.31</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>178</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Medical Psychotherapy Service</t>
+          <t>Clinical Psychology Service</t>
         </is>
       </c>
       <c r="B81">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D81">
-        <v>1.73</v>
+        <v>7.69</v>
       </c>
       <c r="E81">
         <v>1</v>
       </c>
       <c r="F81">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G81">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Old Age Psychiatry Service</t>
+          <t>Prosthetics Service</t>
         </is>
       </c>
       <c r="B82">
-        <v>1422</v>
+        <v>6</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>5.53</v>
+        <v>0.58</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="G82">
-        <v>464</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Liaison Psychiatry Service</t>
+          <t>Orthotics Service</t>
         </is>
       </c>
       <c r="B83">
-        <v>88</v>
+        <v>481</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D83">
-        <v>3.42</v>
+        <v>1.49</v>
       </c>
       <c r="E83">
         <v>1</v>
       </c>
       <c r="F83">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G83">
-        <v>28</v>
+        <v>252</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Clinical Oncology Service</t>
+          <t>Optometry Service</t>
         </is>
       </c>
       <c r="B84">
-        <v>586</v>
+        <v>54</v>
       </c>
       <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84">
+        <v>0.9</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="F84">
         <v>4</v>
       </c>
-      <c r="D84">
-        <v>6.61</v>
-      </c>
-      <c r="E84">
-        <v>1</v>
-      </c>
-      <c r="F84">
-        <v>39</v>
-      </c>
       <c r="G84">
-        <v>133</v>
+        <v>37</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Interventional Radiology Service</t>
+          <t>Podiatric Surgery Service</t>
         </is>
       </c>
       <c r="B85">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85">
-        <v>0.27</v>
+        <v>2.37</v>
       </c>
       <c r="E85">
         <v>1</v>
       </c>
       <c r="F85">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G85">
-        <v>172</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging Service</t>
+          <t>Learning Disability Service</t>
         </is>
       </c>
       <c r="B86">
-        <v>5698</v>
+        <v>334</v>
       </c>
       <c r="C86">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D86">
-        <v>1.82</v>
+        <v>14.03</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
       <c r="F86">
+        <v>69</v>
+      </c>
+      <c r="G86">
         <v>41</v>
-      </c>
-      <c r="G86">
-        <v>2933</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Chemical Pathology Service</t>
+          <t>Adult Mental Health Service</t>
         </is>
       </c>
       <c r="B87">
-        <v>101</v>
+        <v>1030</v>
       </c>
       <c r="C87">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D87">
-        <v>1.82</v>
+        <v>11.94</v>
       </c>
       <c r="E87">
         <v>1</v>
       </c>
       <c r="F87">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="G87">
-        <v>37</v>
+        <v>192</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>Child and Adolescent Psychiatry Service</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>3</v>
+      </c>
+      <c r="C88">
+        <v>3</v>
+      </c>
+      <c r="E88">
+        <v>3</v>
+      </c>
+      <c r="F88">
+        <v>3</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Medical Psychotherapy Service</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>6</v>
+      </c>
+      <c r="C89">
+        <v>2</v>
+      </c>
+      <c r="D89">
+        <v>1.73</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>4</v>
+      </c>
+      <c r="G89">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Old Age Psychiatry Service</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>1422</v>
+      </c>
+      <c r="C90">
+        <v>3</v>
+      </c>
+      <c r="D90">
+        <v>5.53</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <v>64</v>
+      </c>
+      <c r="G90">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Liaison Psychiatry Service</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>88</v>
+      </c>
+      <c r="C91">
+        <v>3</v>
+      </c>
+      <c r="D91">
+        <v>3.42</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="F91">
+        <v>14</v>
+      </c>
+      <c r="G91">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Clinical Oncology Service</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>586</v>
+      </c>
+      <c r="C92">
+        <v>4</v>
+      </c>
+      <c r="D92">
+        <v>6.61</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92">
+        <v>39</v>
+      </c>
+      <c r="G92">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Interventional Radiology Service</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>183</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93">
+        <v>0.27</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="F93">
+        <v>3</v>
+      </c>
+      <c r="G93">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Diagnostic Imaging Service</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>5698</v>
+      </c>
+      <c r="C94">
+        <v>2</v>
+      </c>
+      <c r="D94">
+        <v>1.82</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94">
+        <v>41</v>
+      </c>
+      <c r="G94">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Chemical Pathology Service</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>101</v>
+      </c>
+      <c r="C95">
+        <v>3</v>
+      </c>
+      <c r="D95">
+        <v>1.82</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95">
+        <v>7</v>
+      </c>
+      <c r="G95">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>Audiology Service</t>
         </is>
       </c>
-      <c r="B88">
+      <c r="B96">
         <v>1883</v>
       </c>
-      <c r="C88">
-        <v>2</v>
-      </c>
-      <c r="D88">
+      <c r="C96">
+        <v>2</v>
+      </c>
+      <c r="D96">
         <v>1.79</v>
       </c>
-      <c r="E88">
-        <v>1</v>
-      </c>
-      <c r="F88">
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96">
         <v>21</v>
       </c>
-      <c r="G88">
+      <c r="G96">
         <v>787</v>
       </c>
     </row>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_appointments_by_tretspef-Users_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_appointments_by_tretspef-Users_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -569,392 +569,392 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ophthalmology Service</t>
+          <t>Trauma and Orthopaedic Service</t>
         </is>
       </c>
       <c r="B9">
-        <v>122772</v>
+        <v>54336</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>7.49</v>
+        <v>2.51</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>213</v>
+        <v>102</v>
       </c>
       <c r="G9">
-        <v>19478</v>
+        <v>16624</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Oral Surgery Service</t>
+          <t>Ear Nose and Throat Service</t>
         </is>
       </c>
       <c r="B10">
-        <v>675</v>
+        <v>2449</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>1.43</v>
+        <v>4.75</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="G10">
-        <v>350</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Restorative Dentistry Service</t>
+          <t>Ophthalmology Service</t>
         </is>
       </c>
       <c r="B11">
-        <v>331</v>
+        <v>11855</v>
       </c>
       <c r="C11">
         <v>4</v>
       </c>
       <c r="D11">
-        <v>3.89</v>
+        <v>4.15</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G11">
-        <v>86</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Orthodontic Service</t>
+          <t>Oral Surgery Service</t>
         </is>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>675</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Maxillofacial Surgery Service</t>
+          <t>Restorative Dentistry Service</t>
         </is>
       </c>
       <c r="B13">
-        <v>536</v>
+        <v>331</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>1.98</v>
+        <v>3.89</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G13">
-        <v>258</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Neurosurgical Service</t>
+          <t>Orthodontic Service</t>
         </is>
       </c>
       <c r="B14">
-        <v>661</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>301</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cardiac Surgery Service</t>
+          <t>Maxillofacial Surgery Service</t>
         </is>
       </c>
       <c r="B15">
-        <v>61</v>
+        <v>536</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G15">
-        <v>35</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Thoracic Surgery Service</t>
+          <t>Neurosurgical Service</t>
         </is>
       </c>
       <c r="B16">
-        <v>38</v>
+        <v>661</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16">
-        <v>0.93</v>
+        <v>2.09</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G16">
-        <v>21</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cardiothoracic Transplantation Service</t>
+          <t>Plastic Surgery Service</t>
         </is>
       </c>
       <c r="B17">
-        <v>56</v>
+        <v>1061</v>
       </c>
       <c r="C17">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>15.7</v>
+        <v>3</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pain Management Service</t>
+          <t>Burns Care Service</t>
         </is>
       </c>
       <c r="B18">
-        <v>1186</v>
+        <v>48</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>2.43</v>
+        <v>6.07</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18">
-        <v>473</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Paediatric Trauma and Orthopaedic Service</t>
+          <t>Cardiothoracic Surgery Service</t>
         </is>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>0.5600000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G19">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Paediatric Ophthalmology Service</t>
+          <t>Cardiac Surgery Service</t>
         </is>
       </c>
       <c r="B20">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gastroenterology Service</t>
+          <t>Thoracic Surgery Service</t>
         </is>
       </c>
       <c r="B21">
-        <v>1813</v>
+        <v>38</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21">
-        <v>1.74</v>
+        <v>0.93</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>949</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Endocrinology Service</t>
+          <t>Cardiothoracic Transplantation Service</t>
         </is>
       </c>
       <c r="B22">
-        <v>586</v>
+        <v>56</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D22">
-        <v>1.8</v>
+        <v>15.7</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G22">
-        <v>269</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Clinical Pharmacology Service</t>
+          <t>Emergency Medicine Service</t>
         </is>
       </c>
       <c r="B23">
-        <v>17</v>
+        <v>378</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>2.15</v>
+        <v>1.17</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G23">
-        <v>7</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hepatology Service</t>
+          <t>Anaesthetic Service</t>
         </is>
       </c>
       <c r="B24">
-        <v>144</v>
+        <v>480</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>1.15</v>
+        <v>0.62</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -963,71 +963,71 @@
         <v>5</v>
       </c>
       <c r="G24">
-        <v>70</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Diabetes Service</t>
+          <t>Pain Management Service</t>
         </is>
       </c>
       <c r="B25">
-        <v>929</v>
+        <v>1186</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
       <c r="D25">
-        <v>5.22</v>
+        <v>2.43</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="G25">
-        <v>268</v>
+        <v>473</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Blood and Marrow Transplantation Service</t>
+          <t>Paediatric Trauma and Orthopaedic Service</t>
         </is>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
+      <c r="D26">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Clinical Genetics Service</t>
+          <t>Paediatric Ear Nose and Throat Service</t>
         </is>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
       <c r="E27">
         <v>1</v>
       </c>
@@ -1035,23 +1035,23 @@
         <v>1</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Clinical Immunology Service</t>
+          <t>Paediatric Ophthalmology Service</t>
         </is>
       </c>
       <c r="B28">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -1060,592 +1060,592 @@
         <v>7</v>
       </c>
       <c r="G28">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Intermediate Care Service</t>
+          <t>General Internal Medicine Service</t>
         </is>
       </c>
       <c r="B29">
-        <v>2238</v>
+        <v>4483</v>
       </c>
       <c r="C29">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>22.54</v>
+        <v>12.38</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>148</v>
+        <v>201</v>
       </c>
       <c r="G29">
-        <v>168</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cardiology Service</t>
+          <t>Gastroenterology Service</t>
         </is>
       </c>
       <c r="B30">
-        <v>4309</v>
+        <v>1813</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
       <c r="D30">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G30">
-        <v>2015</v>
+        <v>949</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Clinical Microbiology Service</t>
+          <t>Endocrinology Service</t>
         </is>
       </c>
       <c r="B31">
-        <v>10</v>
+        <v>586</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>0.79</v>
+        <v>1.8</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G31">
-        <v>7</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Anticoagulant Service</t>
+          <t>Clinical Haematology Service</t>
         </is>
       </c>
       <c r="B32">
-        <v>2976</v>
+        <v>1600</v>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D32">
-        <v>11.68</v>
+        <v>4.06</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="G32">
-        <v>298</v>
+        <v>477</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sport and Exercise Medicine Service</t>
+          <t>Clinical Pharmacology Service</t>
         </is>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>2.15</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Stroke Medicine Service</t>
+          <t>Hepatology Service</t>
         </is>
       </c>
       <c r="B34">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>0.76</v>
+        <v>1.15</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G34">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dermatology Service</t>
+          <t>Diabetes Service</t>
         </is>
       </c>
       <c r="B35">
-        <v>2835</v>
+        <v>929</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35">
-        <v>4.19</v>
+        <v>5.22</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G35">
-        <v>1118</v>
+        <v>268</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Respiratory Physiology Service</t>
+          <t>Blood and Marrow Transplantation Service</t>
         </is>
       </c>
       <c r="B36">
-        <v>225</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>2</v>
-      </c>
-      <c r="D36">
-        <v>1.51</v>
+        <v>1</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tropical Medicine Service</t>
+          <t>Haemophilia Service</t>
         </is>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Genitourinary Medicine Service</t>
+          <t>Clinical Genetics Service</t>
         </is>
       </c>
       <c r="B38">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Renal Medicine Service</t>
+          <t>Clinical Immunology and Allergy Service</t>
         </is>
       </c>
       <c r="B39">
-        <v>959</v>
+        <v>47</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D39">
-        <v>4.14</v>
+        <v>1.81</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G39">
-        <v>259</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Medical Oncology Service</t>
+          <t>Rehabilitation Medicine Service</t>
         </is>
       </c>
       <c r="B40">
-        <v>298</v>
+        <v>1378</v>
       </c>
       <c r="C40">
         <v>4</v>
       </c>
       <c r="D40">
-        <v>6.91</v>
+        <v>6.2</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
       <c r="F40">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="G40">
-        <v>73</v>
+        <v>318</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nuclear Medicine Service</t>
+          <t>Palliative Medicine Service</t>
         </is>
       </c>
       <c r="B41">
-        <v>55</v>
+        <v>212</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D41">
-        <v>1.46</v>
+        <v>12.45</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="F41">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="G41">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Neurology Service</t>
+          <t>Clinical Immunology Service</t>
         </is>
       </c>
       <c r="B42">
-        <v>1700</v>
+        <v>32</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G42">
-        <v>762</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Rheumatology Service</t>
+          <t>Allergy Service</t>
         </is>
       </c>
       <c r="B43">
-        <v>5236</v>
+        <v>77</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D43">
-        <v>2.87</v>
+        <v>13.43</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G43">
-        <v>2194</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Elderly Medicine Service</t>
+          <t>Intermediate Care Service</t>
         </is>
       </c>
       <c r="B44">
-        <v>3208</v>
+        <v>2248</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D44">
-        <v>4.25</v>
+        <v>22.16</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
       <c r="F44">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="G44">
-        <v>1345</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Occupational Therapy Service</t>
+          <t>Cardiology Service</t>
         </is>
       </c>
       <c r="B45">
-        <v>2747</v>
+        <v>4309</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D45">
-        <v>6.81</v>
+        <v>2.05</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="G45">
-        <v>616</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Podiatry Service</t>
+          <t>Clinical Microbiology Service</t>
         </is>
       </c>
       <c r="B46">
-        <v>1509</v>
+        <v>10</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>4.54</v>
+        <v>0.79</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
       <c r="F46">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G46">
-        <v>372</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Orthoptics Service</t>
+          <t>Spinal Injuries Service</t>
         </is>
       </c>
       <c r="B47">
-        <v>328</v>
+        <v>435</v>
       </c>
       <c r="C47">
         <v>2</v>
       </c>
       <c r="D47">
-        <v>1.31</v>
+        <v>2.16</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G47">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Clinical Psychology Service</t>
+          <t>Anticoagulant Service</t>
         </is>
       </c>
       <c r="B48">
-        <v>97</v>
+        <v>2976</v>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D48">
-        <v>7.69</v>
+        <v>11.68</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="G48">
-        <v>19</v>
+        <v>298</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Optometry Service</t>
+          <t>Sport and Exercise Medicine Service</t>
         </is>
       </c>
       <c r="B49">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49">
         <v>4</v>
       </c>
       <c r="G49">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Child and Adolescent Psychiatry Service</t>
+          <t>Cardiac Rehabilitation Service</t>
         </is>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="D50">
+        <v>7.88</v>
       </c>
       <c r="E50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Medical Psychotherapy Service</t>
+          <t>Stroke Medicine Service</t>
         </is>
       </c>
       <c r="B51">
+        <v>75</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>0.76</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51">
         <v>6</v>
       </c>
-      <c r="C51">
-        <v>2</v>
-      </c>
-      <c r="D51">
-        <v>1.73</v>
-      </c>
-      <c r="E51">
-        <v>1</v>
-      </c>
-      <c r="F51">
-        <v>4</v>
-      </c>
       <c r="G51">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Interventional Radiology Service</t>
+          <t>Transient Ischaemic Attack Service</t>
         </is>
       </c>
       <c r="B52">
-        <v>304</v>
+        <v>141</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
       <c r="D52">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -1654,32 +1654,1054 @@
         <v>4</v>
       </c>
       <c r="G52">
-        <v>251</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Dermatology Service</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>2835</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53">
+        <v>4.19</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>69</v>
+      </c>
+      <c r="G53">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Congenital Heart Disease Service</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>6</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54">
+        <v>2.83</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>5</v>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Respiratory Medicine Service</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>2504</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55">
+        <v>4.06</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>67</v>
+      </c>
+      <c r="G55">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Respiratory Physiology Service</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>225</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56">
+        <v>1.51</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>10</v>
+      </c>
+      <c r="G56">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Pulmonary Rehabilitation Service</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>10</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57">
+        <v>1.21</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>4</v>
+      </c>
+      <c r="G57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>20</v>
+      </c>
+      <c r="C58">
+        <v>4</v>
+      </c>
+      <c r="D58">
+        <v>4.58</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>12</v>
+      </c>
+      <c r="G58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Infectious Diseases Service</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>58</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59">
+        <v>2.1</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>8</v>
+      </c>
+      <c r="G59">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Tropical Medicine Service</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>3</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Genitourinary Medicine Service</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>11</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61">
+        <v>1.17</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>4</v>
+      </c>
+      <c r="G61">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Renal Medicine Service</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>959</v>
+      </c>
+      <c r="C62">
+        <v>4</v>
+      </c>
+      <c r="D62">
+        <v>4.14</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>27</v>
+      </c>
+      <c r="G62">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Medical Oncology Service</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>298</v>
+      </c>
+      <c r="C63">
+        <v>4</v>
+      </c>
+      <c r="D63">
+        <v>6.91</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>49</v>
+      </c>
+      <c r="G63">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Nuclear Medicine Service</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>55</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64">
+        <v>1.46</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>8</v>
+      </c>
+      <c r="G64">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Neurology Service</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>1700</v>
+      </c>
+      <c r="C65">
+        <v>2</v>
+      </c>
+      <c r="D65">
+        <v>2.29</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>26</v>
+      </c>
+      <c r="G65">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Clinical Neurophysiology Service</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>255</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66">
+        <v>0.51</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+      <c r="G66">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Rheumatology Service</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>5236</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+      <c r="D67">
+        <v>2.87</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>58</v>
+      </c>
+      <c r="G67">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Paediatric Service</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Elderly Medicine Service</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>3208</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
+      <c r="D69">
+        <v>4.25</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="F69">
+        <v>92</v>
+      </c>
+      <c r="G69">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Dental Medicine Service</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>130</v>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+      <c r="D70">
+        <v>2.13</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>13</v>
+      </c>
+      <c r="G70">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Obstetrics Service</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>4</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Gynaecology Service</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>2016</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="D72">
+        <v>1.82</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+      <c r="F72">
+        <v>22</v>
+      </c>
+      <c r="G72">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Gynaecological Oncology Service</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>199</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+      <c r="D73">
+        <v>1.66</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+      <c r="F73">
+        <v>14</v>
+      </c>
+      <c r="G73">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Physiotherapy Service</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>26485</v>
+      </c>
+      <c r="C74">
+        <v>5</v>
+      </c>
+      <c r="D74">
+        <v>5.1</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>109</v>
+      </c>
+      <c r="G74">
+        <v>5351</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Occupational Therapy Service</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>2747</v>
+      </c>
+      <c r="C75">
+        <v>4</v>
+      </c>
+      <c r="D75">
+        <v>6.81</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+      <c r="F75">
+        <v>84</v>
+      </c>
+      <c r="G75">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Speech and Language Therapy Service</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>211</v>
+      </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+      <c r="D76">
+        <v>2.67</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <v>20</v>
+      </c>
+      <c r="G76">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Podiatry Service</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>1509</v>
+      </c>
+      <c r="C77">
+        <v>4</v>
+      </c>
+      <c r="D77">
+        <v>4.54</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <v>32</v>
+      </c>
+      <c r="G77">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Dietetics Service</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>622</v>
+      </c>
+      <c r="C78">
+        <v>3</v>
+      </c>
+      <c r="D78">
+        <v>3.49</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+      <c r="F78">
+        <v>38</v>
+      </c>
+      <c r="G78">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Orthoptics Service</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>328</v>
+      </c>
+      <c r="C79">
+        <v>2</v>
+      </c>
+      <c r="D79">
+        <v>1.31</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="F79">
+        <v>8</v>
+      </c>
+      <c r="G79">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Clinical Psychology Service</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>845</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>2.01</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="F80">
+        <v>38</v>
+      </c>
+      <c r="G80">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Prosthetics Service</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>6</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+      <c r="D81">
+        <v>0.58</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="F81">
+        <v>2</v>
+      </c>
+      <c r="G81">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Orthotics Service</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>481</v>
+      </c>
+      <c r="C82">
+        <v>2</v>
+      </c>
+      <c r="D82">
+        <v>1.49</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="F82">
+        <v>12</v>
+      </c>
+      <c r="G82">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Optometry Service</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>54</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>0.9</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="F83">
+        <v>4</v>
+      </c>
+      <c r="G83">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Podiatric Surgery Service</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>44</v>
+      </c>
+      <c r="C84">
+        <v>3</v>
+      </c>
+      <c r="D84">
+        <v>2.37</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="F84">
+        <v>9</v>
+      </c>
+      <c r="G84">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Learning Disability Service</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>334</v>
+      </c>
+      <c r="C85">
+        <v>8</v>
+      </c>
+      <c r="D85">
+        <v>14.03</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85">
+        <v>69</v>
+      </c>
+      <c r="G85">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Child and Adolescent Psychiatry Service</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>3</v>
+      </c>
+      <c r="C86">
+        <v>3</v>
+      </c>
+      <c r="E86">
+        <v>3</v>
+      </c>
+      <c r="F86">
+        <v>3</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Medical Psychotherapy Service</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>6</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87">
+        <v>1.73</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+      <c r="F87">
+        <v>4</v>
+      </c>
+      <c r="G87">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Old Age Psychiatry Service</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>1422</v>
+      </c>
+      <c r="C88">
+        <v>3</v>
+      </c>
+      <c r="D88">
+        <v>5.53</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="F88">
+        <v>64</v>
+      </c>
+      <c r="G88">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Liaison Psychiatry Service</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>1118</v>
+      </c>
+      <c r="C89">
+        <v>5</v>
+      </c>
+      <c r="D89">
+        <v>11.24</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>113</v>
+      </c>
+      <c r="G89">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Clinical Oncology Service</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>586</v>
+      </c>
+      <c r="C90">
+        <v>4</v>
+      </c>
+      <c r="D90">
+        <v>6.61</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <v>39</v>
+      </c>
+      <c r="G90">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Interventional Radiology Service</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>304</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91">
+        <v>0.57</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="F91">
+        <v>4</v>
+      </c>
+      <c r="G91">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Diagnostic Imaging Service</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>5698</v>
+      </c>
+      <c r="C92">
+        <v>2</v>
+      </c>
+      <c r="D92">
+        <v>1.82</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92">
+        <v>41</v>
+      </c>
+      <c r="G92">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Chemical Pathology Service</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>101</v>
+      </c>
+      <c r="C93">
+        <v>3</v>
+      </c>
+      <c r="D93">
+        <v>1.82</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="F93">
+        <v>7</v>
+      </c>
+      <c r="G93">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>Audiology Service</t>
         </is>
       </c>
-      <c r="B53">
-        <v>1883</v>
-      </c>
-      <c r="C53">
-        <v>2</v>
-      </c>
-      <c r="D53">
-        <v>1.79</v>
-      </c>
-      <c r="E53">
-        <v>1</v>
-      </c>
-      <c r="F53">
+      <c r="B94">
+        <v>2430</v>
+      </c>
+      <c r="C94">
+        <v>2</v>
+      </c>
+      <c r="D94">
+        <v>1.76</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94">
         <v>21</v>
       </c>
-      <c r="G53">
-        <v>787</v>
+      <c r="G94">
+        <v>1006</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_appointments_by_tretspef-Users_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_appointments_by_tretspef-Users_OMOP.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>54336</v>
+        <v>54293</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -588,7 +588,7 @@
         <v>102</v>
       </c>
       <c r="G9">
-        <v>16624</v>
+        <v>16620</v>
       </c>
     </row>
     <row r="10">
